--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R40a9b70b00f14e66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R3e135ee847c14710"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -342,15 +342,15 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>脱敏lockfile、许可证策略、离线漏洞摘要和owner映射</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="33" customHeight="1">
+        <x:v>本次发布裁决使用的lockfile、许可证策略、离线漏洞摘要和owner映射，字段已经脱敏</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="4" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>数据装载</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>解压输入数据包后在input_data目录读取本地材料</x:v>
+        <x:v>Node.js入口读取package-lock.json、owners.csv、license_policy.json和vulnerability_feed.json，并加载完成版审计程序</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="63" customHeight="1">
@@ -371,10 +371,10 @@
     </x:row>
     <x:row r="9" ht="33" customHeight="1">
       <x:c r="A9" s="4" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>发布目标</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>遍历依赖图；分派owner；归一许可证；连接漏洞；计算例外；形成裁决；导出报告</x:v>
+        <x:v>厘清应用依赖及负责人，归一许可证处置，核对漏洞例外和门禁动作，并给出本次版本的发布裁决</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="33" customHeight="1">
@@ -427,34 +427,34 @@
     </x:row>
     <x:row r="16" ht="33" customHeight="1">
       <x:c r="A16" s="4" t="str">
-        <x:v>离线边界</x:v>
+        <x:v>Node.js执行边界</x:v>
       </x:c>
       <x:c r="B16" s="4" t="str">
-        <x:v>正式处理不访问registry、漏洞服务、许可证服务或发布平台</x:v>
+        <x:v>依赖图遍历、owner继承、策略关联、UTC日期判断和发布裁决均由完成版Node.js程序执行</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
       <x:c r="A17" s="4" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>报告交接</x:v>
       </x:c>
       <x:c r="B17" s="4" t="str">
-        <x:v>Node.js入口返回0，声明的程序和报告可读，依赖、许可、漏洞、owner与发布结论能够互相追溯</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="33" customHeight="1">
+        <x:v>依赖清单交给发布工程，许可证处置交给开源合规，漏洞门禁交给安全运营，release_decision.json交给发布负责人</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="48" customHeight="1">
       <x:c r="A18" s="4" t="str">
-        <x:v>结果核对</x:v>
+        <x:v>结果追溯</x:v>
       </x:c>
       <x:c r="B18" s="4" t="str">
-        <x:v>依赖路径、父子关系、许可证状态、例外状态、门禁动作和发布集合可从输入复算</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="33" customHeight="1">
+        <x:v>依赖路径与父子关系来自lockfile，owner来自映射规则，许可证状态来自策略，漏洞动作来自摘要、报告日期和例外期限；正式处理不访问registry或外部服务</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="48" customHeight="1">
       <x:c r="A19" s="4" t="str">
-        <x:v>实现自由度</x:v>
+        <x:v>等价实现边界</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>函数拆分、遍历容器、对象键序、CSV引号和本机路径可以不同</x:v>
+        <x:v>函数拆分、遍历容器和对象键序可以不同；依赖主键、父子关系、owner、许可证处置、漏洞动作和发布集合保持一致</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
